--- a/Datos/turismo.xlsx
+++ b/Datos/turismo.xlsx
@@ -8,17 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1. MECA\2025\EVALUACIACÓN DE IMPACTO- Raachid Raaj\Trabajo final\Trabajo-Final--Evaluaci-n-de-impacto\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70764E96-9C65-437E-A1BC-10892491E1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0296F85-818D-4A0C-967E-7C446DA45A88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-2265" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Códigos DANE Municipios" sheetId="2" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <definedNames>
     <definedName name="ESCOLARIDAD">#REF!</definedName>
     <definedName name="ESTADOCIVIL">#REF!</definedName>
@@ -36,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2256" uniqueCount="2171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3997" uniqueCount="2332">
   <si>
     <t>Codmpio</t>
   </si>
@@ -6548,7 +6545,490 @@
     <t>CUMARIBO</t>
   </si>
   <si>
-    <t>bogota</t>
+    <t>SANTA ROSALIA</t>
+  </si>
+  <si>
+    <t>ABREGO</t>
+  </si>
+  <si>
+    <t>ABRIAQUI</t>
+  </si>
+  <si>
+    <t>ACACIAS</t>
+  </si>
+  <si>
+    <t>ACANDI</t>
+  </si>
+  <si>
+    <t>ACHI</t>
+  </si>
+  <si>
+    <t>AGUSTIN CODAZZI</t>
+  </si>
+  <si>
+    <t>ALBAN</t>
+  </si>
+  <si>
+    <t>ALCALA</t>
+  </si>
+  <si>
+    <t>ALEJANDRIA</t>
+  </si>
+  <si>
+    <t>AMAGA</t>
+  </si>
+  <si>
+    <t>ANDALUCIA</t>
+  </si>
+  <si>
+    <t>ANORI</t>
+  </si>
+  <si>
+    <t>ANTIOQUIA</t>
+  </si>
+  <si>
+    <t>APARTADO</t>
+  </si>
+  <si>
+    <t>APIA</t>
+  </si>
+  <si>
+    <t>ARIGUANI</t>
+  </si>
+  <si>
+    <t>ARJOMA</t>
+  </si>
+  <si>
+    <t>ARMERO</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>BAGADO</t>
+  </si>
+  <si>
+    <t>BAHIA SOLANO</t>
+  </si>
+  <si>
+    <t>BAJO BAUDO</t>
+  </si>
+  <si>
+    <t>BARRANCA DE UPIA</t>
+  </si>
+  <si>
+    <t>BARRANCABERBJA</t>
+  </si>
+  <si>
+    <t>BELALCAZAR</t>
+  </si>
+  <si>
+    <t>BELEN</t>
+  </si>
+  <si>
+    <t>BELEN DE UMBRIA</t>
+  </si>
+  <si>
+    <t>BELTRAN</t>
+  </si>
+  <si>
+    <t>BOGOTA D.C</t>
+  </si>
+  <si>
+    <t>BOJACA</t>
+  </si>
+  <si>
+    <t>BOLIVAR</t>
+  </si>
+  <si>
+    <t>BOYACA</t>
+  </si>
+  <si>
+    <t>BUGA</t>
+  </si>
+  <si>
+    <t>BURITICA</t>
+  </si>
+  <si>
+    <t>CACERES</t>
+  </si>
+  <si>
+    <t>CACHIRA</t>
+  </si>
+  <si>
+    <t>CACOTA</t>
+  </si>
+  <si>
+    <t>CAJIBIO</t>
+  </si>
+  <si>
+    <t>CAJICA</t>
+  </si>
+  <si>
+    <t>CALARCA</t>
+  </si>
+  <si>
+    <t>CAPARRAPI</t>
+  </si>
+  <si>
+    <t>CAQUEZA</t>
+  </si>
+  <si>
+    <t>CARACOLI</t>
+  </si>
+  <si>
+    <t>CARMEN DE APIC</t>
+  </si>
+  <si>
+    <t>CARMEN DE VIBO</t>
+  </si>
+  <si>
+    <t>CARTAGENA</t>
+  </si>
+  <si>
+    <t>CARTAGENA DEL</t>
+  </si>
+  <si>
+    <t>CARURU</t>
+  </si>
+  <si>
+    <t>CEPITA</t>
+  </si>
+  <si>
+    <t>CERETE</t>
+  </si>
+  <si>
+    <t>CHACHAGUI</t>
+  </si>
+  <si>
+    <t>CHAGUANI</t>
+  </si>
+  <si>
+    <t>CHARALA</t>
+  </si>
+  <si>
+    <t>CHIA</t>
+  </si>
+  <si>
+    <t>CHINACOTA</t>
+  </si>
+  <si>
+    <t>CHINCHINA</t>
+  </si>
+  <si>
+    <t>CHINU</t>
+  </si>
+  <si>
+    <t>CHIQUINQUIRA</t>
+  </si>
+  <si>
+    <t>CHIRIGUANA</t>
+  </si>
+  <si>
+    <t>CHITAGA</t>
+  </si>
+  <si>
+    <t>CHOACHI</t>
+  </si>
+  <si>
+    <t>CHOCONTA</t>
+  </si>
+  <si>
+    <t>CIENAGA</t>
+  </si>
+  <si>
+    <t>CIENAGA DE ORO</t>
+  </si>
+  <si>
+    <t>COCORNA</t>
+  </si>
+  <si>
+    <t>COLON</t>
+  </si>
+  <si>
+    <t>CONCEPCION</t>
+  </si>
+  <si>
+    <t>CONSACA</t>
+  </si>
+  <si>
+    <t>CORDOBA</t>
+  </si>
+  <si>
+    <t>CURABA</t>
+  </si>
+  <si>
+    <t>CURBARRAL</t>
+  </si>
+  <si>
+    <t>CUCUNUBA</t>
+  </si>
+  <si>
+    <t>CUCUTA</t>
+  </si>
+  <si>
+    <t>CUITIVA</t>
+  </si>
+  <si>
+    <t>CURITI</t>
+  </si>
+  <si>
+    <t>CURUMANI</t>
+  </si>
+  <si>
+    <t>DISTRACCION</t>
+  </si>
+  <si>
+    <t>DON MATIAS</t>
+  </si>
+  <si>
+    <t>DOS QUEBRADAS</t>
+  </si>
+  <si>
+    <t>EBEJICO</t>
+  </si>
+  <si>
+    <t>EL CARMEN DE B</t>
+  </si>
+  <si>
+    <t>EL PAUJIL</t>
+  </si>
+  <si>
+    <t>EL PENON</t>
+  </si>
+  <si>
+    <t>EL PLAYON</t>
+  </si>
+  <si>
+    <t>ELIAS</t>
+  </si>
+  <si>
+    <t>ENTRERRIOS</t>
+  </si>
+  <si>
+    <t>FACATATIVA</t>
+  </si>
+  <si>
+    <t>FLORIAN</t>
+  </si>
+  <si>
+    <t>FUNDACION</t>
+  </si>
+  <si>
+    <t>FUSAGASUGA</t>
+  </si>
+  <si>
+    <t>GACHANCIPA</t>
+  </si>
+  <si>
+    <t>GACHANTIVA</t>
+  </si>
+  <si>
+    <t>GALAN</t>
+  </si>
+  <si>
+    <t>GALAGA</t>
+  </si>
+  <si>
+    <t>GARZON</t>
+  </si>
+  <si>
+    <t>GENOVA</t>
+  </si>
+  <si>
+    <t>GIRON</t>
+  </si>
+  <si>
+    <t>GOMEZ PLATA</t>
+  </si>
+  <si>
+    <t>GRANADA (ANTIOQUIA)</t>
+  </si>
+  <si>
+    <t>GRANADA (CUNDI)</t>
+  </si>
+  <si>
+    <t>GRANADA (META</t>
+  </si>
+  <si>
+    <t>GUACARI</t>
+  </si>
+  <si>
+    <t>GUAPI</t>
+  </si>
+  <si>
+    <t>GUATAPE</t>
+  </si>
+  <si>
+    <t>GUATICA</t>
+  </si>
+  <si>
+    <t>GUAYATA</t>
+  </si>
+  <si>
+    <t>GUEPSA</t>
+  </si>
+  <si>
+    <t>GUICAN</t>
+  </si>
+  <si>
+    <t>GONDA</t>
+  </si>
+  <si>
+    <t>IBAGUE</t>
+  </si>
+  <si>
+    <t>ICUIRA</t>
+  </si>
+  <si>
+    <t>INZA</t>
+  </si>
+  <si>
+    <t>ITAGUI</t>
+  </si>
+  <si>
+    <t>JAMUNDI</t>
+  </si>
+  <si>
+    <t>JARDIN</t>
+  </si>
+  <si>
+    <t>JERICO</t>
+  </si>
+  <si>
+    <t>JURADO</t>
+  </si>
+  <si>
+    <t>LA CHORERA</t>
+  </si>
+  <si>
+    <t>LA JAGUA DE IBIRI</t>
+  </si>
+  <si>
+    <t>LA UNION</t>
+  </si>
+  <si>
+    <t>LA URIBE</t>
+  </si>
+  <si>
+    <t>LABRIJA</t>
+  </si>
+  <si>
+    <t>LERIDA</t>
+  </si>
+  <si>
+    <t>LIBANO</t>
+  </si>
+  <si>
+    <t>MACHETA</t>
+  </si>
+  <si>
+    <t>MAGANGUE</t>
+  </si>
+  <si>
+    <t>MALAGA</t>
+  </si>
+  <si>
+    <t>MANAURE BALCO</t>
+  </si>
+  <si>
+    <t>MANI</t>
+  </si>
+  <si>
+    <t>MAPIRIPAN</t>
+  </si>
+  <si>
+    <t>MARIQUITA</t>
+  </si>
+  <si>
+    <t>MEDELLIN</t>
+  </si>
+  <si>
+    <t>MISTRATO</t>
+  </si>
+  <si>
+    <t>MITU</t>
+  </si>
+  <si>
+    <t>MOMPOS</t>
+  </si>
+  <si>
+    <t>MONIQUIRA</t>
+  </si>
+  <si>
+    <t>MONITOS</t>
+  </si>
+  <si>
+    <t>MONTELIBANO</t>
+  </si>
+  <si>
+    <t>MONTERIA</t>
+  </si>
+  <si>
+    <t>MUTATA</t>
+  </si>
+  <si>
+    <t>NECOCLI</t>
+  </si>
+  <si>
+    <t>NEMOCON</t>
+  </si>
+  <si>
+    <t>NUNCHIA</t>
+  </si>
+  <si>
+    <t>NUQUI</t>
+  </si>
+  <si>
+    <t>OROCUE</t>
+  </si>
+  <si>
+    <t>PACORA</t>
+  </si>
+  <si>
+    <t>PATIA (el bordo)</t>
+  </si>
+  <si>
+    <t>PAZ DE RIO</t>
+  </si>
+  <si>
+    <t>PIENDAMO</t>
+  </si>
+  <si>
+    <t>PIOJO</t>
+  </si>
+  <si>
+    <t>POPAYAN</t>
+  </si>
+  <si>
+    <t>PTO NAREL(LAMAG</t>
+  </si>
+  <si>
+    <t>PUERTO ASIS</t>
+  </si>
+  <si>
+    <t>PUERTO BERRIO</t>
+  </si>
+  <si>
+    <t>PUERTO BOYACA</t>
+  </si>
+  <si>
+    <t>PUERTO CONCOR</t>
+  </si>
+  <si>
+    <t>PUERTO GAITAN</t>
+  </si>
+  <si>
+    <t>PUERTO INIRIDA</t>
+  </si>
+  <si>
+    <t>PUERTO LEGUIZA</t>
+  </si>
+  <si>
+    <t>PUERTO LIBERTAD</t>
+  </si>
+  <si>
+    <t>PUERTO LOPEZ</t>
   </si>
 </sst>
 </file>
@@ -6572,7 +7052,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6582,6 +7062,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6613,7 +7105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6627,6 +7119,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6643,28 +7147,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="FORMATO_CENSOS"/>
-      <sheetName val="Convenciones"/>
-      <sheetName val="Códigos DANE Departamentos"/>
-      <sheetName val="Códigos DANE Municipios"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15929,44 +16411,6349 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J441"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="29" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C2">
+        <v>2013</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
         <v>2170</v>
+      </c>
+      <c r="C3">
+        <v>2013</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>2013</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C5">
+        <v>2013</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>2172</v>
+      </c>
+      <c r="C6">
+        <v>2013</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C7">
+        <v>2013</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>2174</v>
+      </c>
+      <c r="C8">
+        <v>2013</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C9">
+        <v>2013</v>
+      </c>
+      <c r="G9">
+        <v>829</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>2175</v>
+      </c>
+      <c r="C10">
+        <v>2013</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="J10" s="9"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>916</v>
+      </c>
+      <c r="C11">
+        <v>2013</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>810</v>
+      </c>
+      <c r="C12">
+        <v>2013</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C13">
+        <v>2013</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>2050</v>
+      </c>
+      <c r="C14">
+        <v>2013</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C15">
+        <v>2013</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C16">
+        <v>2013</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C17">
+        <v>2013</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>700</v>
+      </c>
+      <c r="C18">
+        <v>2013</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>2178</v>
+      </c>
+      <c r="C19">
+        <v>2013</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>2179</v>
+      </c>
+      <c r="C20">
+        <v>2013</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C21">
+        <v>2013</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C22">
+        <v>2013</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C23">
+        <v>2013</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C24">
+        <v>2013</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25">
+        <v>2013</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C26">
+        <v>2013</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>920</v>
+      </c>
+      <c r="C27">
+        <v>2013</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>2181</v>
+      </c>
+      <c r="C28">
+        <v>2013</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29">
+        <v>2013</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30">
+        <v>2013</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>922</v>
+      </c>
+      <c r="C31">
+        <v>2013</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C32">
+        <v>2013</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>648</v>
+      </c>
+      <c r="C33">
+        <v>2013</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>1963</v>
+      </c>
+      <c r="C34">
+        <v>2013</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C35">
+        <v>2013</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C36">
+        <v>2013</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C37">
+        <v>2013</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>405</v>
+      </c>
+      <c r="C38">
+        <v>2013</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C39">
+        <v>2013</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>650</v>
+      </c>
+      <c r="C40">
+        <v>2013</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C41">
+        <v>2013</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>2034</v>
+      </c>
+      <c r="C42">
+        <v>2013</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C43">
+        <v>2013</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44">
+        <v>2013</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>407</v>
+      </c>
+      <c r="C45">
+        <v>2013</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46">
+        <v>2013</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>2186</v>
+      </c>
+      <c r="C47">
+        <v>2013</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C48">
+        <v>2013</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
+        <v>42</v>
+      </c>
+      <c r="C49">
+        <v>2013</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>2188</v>
+      </c>
+      <c r="C50">
+        <v>2013</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>814</v>
+      </c>
+      <c r="C51">
+        <v>2013</v>
+      </c>
+      <c r="G51" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>860</v>
+      </c>
+      <c r="C52">
+        <v>2013</v>
+      </c>
+      <c r="G52" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>2190</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>2191</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H54" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>2192</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>734</v>
+      </c>
+      <c r="G56" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>264</v>
+      </c>
+      <c r="G57" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>1421</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>44</v>
+      </c>
+      <c r="G59" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H59" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>1663</v>
+      </c>
+      <c r="G60" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>2193</v>
+      </c>
+      <c r="G61" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H61" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>2194</v>
+      </c>
+      <c r="G62" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H62" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>1275</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H63" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>262</v>
+      </c>
+      <c r="G64" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H64" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>2195</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B66" t="s">
+        <v>2196</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H66" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B67" t="s">
+        <v>2197</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H67" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B68" t="s">
+        <v>48</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H68" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I68" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B69" t="s">
+        <v>2198</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H69" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B70" t="s">
+        <v>50</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B71" t="s">
+        <v>52</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B72" t="s">
+        <v>415</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B73" t="s">
+        <v>1535</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B74" t="s">
+        <v>2199</v>
+      </c>
+      <c r="G74">
+        <v>15081</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>2200</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B76" t="s">
+        <v>2201</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>818</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>2202</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>56</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>1655</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>1967</v>
+      </c>
+      <c r="G81">
+        <v>326</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B82" t="s">
+        <v>420</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B83" t="s">
+        <v>1424</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B84" t="s">
+        <v>2203</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B85" t="s">
+        <v>1971</v>
+      </c>
+      <c r="G85" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B86" t="s">
+        <v>2204</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B87" t="s">
+        <v>932</v>
+      </c>
+      <c r="G87" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B88" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B89" t="s">
+        <v>2205</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B90" t="s">
+        <v>934</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B91" t="s">
+        <v>2206</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B92" t="s">
+        <v>2207</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B93" t="s">
+        <v>62</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I93" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B94" t="s">
+        <v>1973</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B95" t="s">
+        <v>1879</v>
+      </c>
+      <c r="G95" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I95" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B96" t="s">
+        <v>2208</v>
+      </c>
+      <c r="G96" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B97" t="s">
+        <v>2209</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I97" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B98" t="s">
+        <v>323</v>
+      </c>
+      <c r="G98" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I98" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B99" t="s">
+        <v>2210</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I99" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B100" t="s">
+        <v>64</v>
+      </c>
+      <c r="G100" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H100" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I100" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B101" t="s">
+        <v>742</v>
+      </c>
+      <c r="G101" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I101" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B102" t="s">
+        <v>1957</v>
+      </c>
+      <c r="G102" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H102" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I102" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B103" t="s">
+        <v>1670</v>
+      </c>
+      <c r="G103" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H103" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I103" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B104" t="s">
+        <v>1975</v>
+      </c>
+      <c r="G104" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H104" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I104" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B105" t="s">
+        <v>744</v>
+      </c>
+      <c r="G105" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I105" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B106" t="s">
+        <v>1215</v>
+      </c>
+      <c r="G106" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H106" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I106" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B107" t="s">
+        <v>268</v>
+      </c>
+      <c r="G107" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I107" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B108" t="s">
+        <v>325</v>
+      </c>
+      <c r="G108" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H108" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I108" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B109" t="s">
+        <v>2211</v>
+      </c>
+      <c r="G109" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I109" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B110" t="s">
+        <v>1672</v>
+      </c>
+      <c r="G110" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H110" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I110" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B111" t="s">
+        <v>2212</v>
+      </c>
+      <c r="G111" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I111" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B112" t="s">
+        <v>2213</v>
+      </c>
+      <c r="G112" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H112" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I112" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
+        <v>2214</v>
+      </c>
+      <c r="G113" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I113" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B114" t="s">
+        <v>2215</v>
+      </c>
+      <c r="G114" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H114" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I114" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B115" t="s">
+        <v>2216</v>
+      </c>
+      <c r="G115">
+        <v>443458</v>
+      </c>
+      <c r="H115" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I115" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B116" t="s">
+        <v>2217</v>
+      </c>
+      <c r="G116" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H116" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I116" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B117" t="s">
+        <v>1978</v>
+      </c>
+      <c r="G117" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H117" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I117" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B118" t="s">
+        <v>2218</v>
+      </c>
+      <c r="G118" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H118" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I118" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B119" t="s">
+        <v>1366</v>
+      </c>
+      <c r="G119" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I119" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B120" t="s">
+        <v>80</v>
+      </c>
+      <c r="G120" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H120" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I120" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>2219</v>
+      </c>
+      <c r="G121" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I121" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B122" t="s">
+        <v>2220</v>
+      </c>
+      <c r="G122" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H122" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I122" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>2221</v>
+      </c>
+      <c r="G123" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I123" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B124" t="s">
+        <v>2222</v>
+      </c>
+      <c r="G124" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H124" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I124" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
+        <v>2223</v>
+      </c>
+      <c r="G125">
+        <v>43</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I125" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>2224</v>
+      </c>
+      <c r="G126" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H126" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I126" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
+        <v>820</v>
+      </c>
+      <c r="G127" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I127" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
+        <v>2225</v>
+      </c>
+      <c r="G128" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H128" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I128" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
+        <v>2226</v>
+      </c>
+      <c r="G129" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H129" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I129" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B130" t="s">
+        <v>2227</v>
+      </c>
+      <c r="G130" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H130" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I130" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
+        <v>948</v>
+      </c>
+      <c r="G131" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H131" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I131" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B132" t="s">
+        <v>2228</v>
+      </c>
+      <c r="G132" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H132" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I132" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B133" t="s">
+        <v>2229</v>
+      </c>
+      <c r="G133" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H133" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I133" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B134" t="s">
+        <v>433</v>
+      </c>
+      <c r="G134" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H134" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I134" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B135" t="s">
+        <v>2230</v>
+      </c>
+      <c r="G135" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H135" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I135" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B136" t="s">
+        <v>459</v>
+      </c>
+      <c r="G136" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H136" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I136" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B137" t="s">
+        <v>2231</v>
+      </c>
+      <c r="G137" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H137" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I137" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B138" t="s">
+        <v>2232</v>
+      </c>
+      <c r="G138" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H138" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I138" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B139" t="s">
+        <v>2233</v>
+      </c>
+      <c r="G139" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H139" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I139" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B140" t="s">
+        <v>2234</v>
+      </c>
+      <c r="G140" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H140" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I140" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="141" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B141" t="s">
+        <v>1688</v>
+      </c>
+      <c r="G141" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H141" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I141" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B142" t="s">
+        <v>1611</v>
+      </c>
+      <c r="G142" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H142" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I142" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B143" t="s">
+        <v>84</v>
+      </c>
+      <c r="G143" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H143" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I143" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>2235</v>
+      </c>
+      <c r="G144" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H144" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I144" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="145" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B145" t="s">
+        <v>84</v>
+      </c>
+      <c r="G145" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H145" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I145" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B146" t="s">
+        <v>2235</v>
+      </c>
+      <c r="G146" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H146" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I146" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="147" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B147" t="s">
+        <v>1887</v>
+      </c>
+      <c r="G147" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H147" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I147" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="148" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B148" t="s">
+        <v>954</v>
+      </c>
+      <c r="G148" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H148" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I148" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="149" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B149" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G149" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H149" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I149" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B150" t="s">
+        <v>2236</v>
+      </c>
+      <c r="G150" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H150" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I150" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B151" t="s">
+        <v>2237</v>
+      </c>
+      <c r="G151" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H151" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I151" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="152" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B152" t="s">
+        <v>90</v>
+      </c>
+      <c r="G152" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H152" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I152" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="153" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B153" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G153" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H153" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I153" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="154" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B154" t="s">
+        <v>2238</v>
+      </c>
+      <c r="G154" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H154" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I154" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="155" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B155" t="s">
+        <v>1430</v>
+      </c>
+      <c r="G155" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H155" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I155" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="156" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B156" t="s">
+        <v>92</v>
+      </c>
+      <c r="G156" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H156" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I156" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="157" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B157" t="s">
+        <v>2239</v>
+      </c>
+      <c r="G157" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H157" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I157" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="158" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B158" t="s">
+        <v>746</v>
+      </c>
+      <c r="G158" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H158" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I158" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="159" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B159" t="s">
+        <v>1823</v>
+      </c>
+      <c r="G159" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H159" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I159" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="160" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B160" t="s">
+        <v>956</v>
+      </c>
+      <c r="G160" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H160" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I160" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B161" t="s">
+        <v>1825</v>
+      </c>
+      <c r="G161" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H161" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I161" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="162" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B162" t="s">
+        <v>2038</v>
+      </c>
+      <c r="G162" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H162" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I162" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B163" t="s">
+        <v>2240</v>
+      </c>
+      <c r="G163" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H163" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I163" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B164" t="s">
+        <v>2241</v>
+      </c>
+      <c r="G164" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H164" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I164" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="165" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B165" t="s">
+        <v>453</v>
+      </c>
+      <c r="G165" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H165" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I165" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="166" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B166" t="s">
+        <v>2242</v>
+      </c>
+      <c r="G166" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H166" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I166" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="167" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B167" t="s">
+        <v>2243</v>
+      </c>
+      <c r="G167" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H167" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I167" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="168" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B168" t="s">
+        <v>1549</v>
+      </c>
+      <c r="G168" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H168" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I168" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="169" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B169" t="s">
+        <v>2244</v>
+      </c>
+      <c r="G169" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H169" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I169" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="170" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B170" t="s">
+        <v>1370</v>
+      </c>
+      <c r="G170" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H170" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I170" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="171" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B171" t="s">
+        <v>2169</v>
+      </c>
+      <c r="G171" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H171" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I171" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="172" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B172" t="s">
+        <v>1435</v>
+      </c>
+      <c r="G172" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H172" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I172" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="173" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B173" t="s">
+        <v>2245</v>
+      </c>
+      <c r="G173" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H173" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I173" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="174" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B174" t="s">
+        <v>2246</v>
+      </c>
+      <c r="G174" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H174" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I174" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="175" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B175" t="s">
+        <v>1980</v>
+      </c>
+      <c r="G175" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H175" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I175" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="176" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B176" t="s">
+        <v>1277</v>
+      </c>
+      <c r="G176" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H176" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I176" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="177" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B177" t="s">
+        <v>2247</v>
+      </c>
+      <c r="G177" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H177" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I177" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="178" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B178" t="s">
+        <v>2248</v>
+      </c>
+      <c r="G178" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H178" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I178" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="179" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B179" t="s">
+        <v>2249</v>
+      </c>
+      <c r="G179" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H179" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I179" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="180" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B180" t="s">
+        <v>461</v>
+      </c>
+      <c r="G180" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H180" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I180" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="181" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B181" t="s">
+        <v>2250</v>
+      </c>
+      <c r="G181" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H181" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I181" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="182" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B182" t="s">
+        <v>100</v>
+      </c>
+      <c r="G182" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H182" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I182" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="183" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B183" t="s">
+        <v>1315</v>
+      </c>
+      <c r="G183" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H183" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I183" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="184" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B184" t="s">
+        <v>1984</v>
+      </c>
+      <c r="G184" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H184" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I184" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="185" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B185" t="s">
+        <v>1553</v>
+      </c>
+      <c r="G185" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H185" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I185" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="186" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B186" t="s">
+        <v>2251</v>
+      </c>
+      <c r="G186" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H186" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I186" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="187" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B187" t="s">
+        <v>1986</v>
+      </c>
+      <c r="G187" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H187" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I187" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="188" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B188" t="s">
+        <v>463</v>
+      </c>
+      <c r="G188">
+        <v>14147</v>
+      </c>
+      <c r="H188" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I188" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="189" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B189" t="s">
+        <v>960</v>
+      </c>
+      <c r="G189" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H189" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I189" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="190" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B190" t="s">
+        <v>826</v>
+      </c>
+      <c r="G190" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H190" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I190" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="191" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B191" t="s">
+        <v>708</v>
+      </c>
+      <c r="G191" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H191" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I191" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="192" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B192" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G192" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H192" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I192" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="193" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B193" t="s">
+        <v>1988</v>
+      </c>
+      <c r="G193" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H193" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I193" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="194" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B194" t="s">
+        <v>828</v>
+      </c>
+      <c r="G194" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H194" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I194" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="195" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B195" t="s">
+        <v>2252</v>
+      </c>
+      <c r="G195" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H195" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I195" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="196" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B196" t="s">
+        <v>2253</v>
+      </c>
+      <c r="G196" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H196" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I196" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="197" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B197" t="s">
+        <v>2254</v>
+      </c>
+      <c r="G197" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H197" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I197" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="198" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B198" t="s">
+        <v>2148</v>
+      </c>
+      <c r="G198" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H198" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I198" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="199" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B199" t="s">
+        <v>963</v>
+      </c>
+      <c r="G199" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H199" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I199" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="200" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B200" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G200" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H200" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I200" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="201" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B201" t="s">
+        <v>1555</v>
+      </c>
+      <c r="G201" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H201" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I201" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="202" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B202" t="s">
+        <v>1557</v>
+      </c>
+      <c r="G202" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H202" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I202" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="203" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B203" t="s">
+        <v>2255</v>
+      </c>
+      <c r="G203" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H203" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I203" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="204" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B204" t="s">
+        <v>2256</v>
+      </c>
+      <c r="G204" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H204" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I204" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="205" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B205" t="s">
+        <v>104</v>
+      </c>
+      <c r="G205" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H205" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I205" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="206" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B206" t="s">
+        <v>1895</v>
+      </c>
+      <c r="G206" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H206" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I206" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="207" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B207" t="s">
+        <v>2257</v>
+      </c>
+      <c r="G207" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H207" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I207" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="208" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B208" t="s">
+        <v>656</v>
+      </c>
+      <c r="G208" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H208" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I208" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="209" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B209" t="s">
+        <v>1614</v>
+      </c>
+      <c r="G209" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H209" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I209" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="210" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B210" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G210" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H210" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I210" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="211" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B211" t="s">
+        <v>698</v>
+      </c>
+      <c r="G211" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H211" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I211" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="212" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B212" t="s">
+        <v>469</v>
+      </c>
+      <c r="G212" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H212" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I212" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="213" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B213" t="s">
+        <v>2258</v>
+      </c>
+      <c r="G213" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H213" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I213" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="214" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B214" t="s">
+        <v>1990</v>
+      </c>
+      <c r="G214" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H214" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I214" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="215" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B215" t="s">
+        <v>1712</v>
+      </c>
+      <c r="G215" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H215" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I215" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="216" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B216" t="s">
+        <v>1283</v>
+      </c>
+      <c r="G216" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H216" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I216" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="217" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B217" t="s">
+        <v>2040</v>
+      </c>
+      <c r="G217" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H217" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I217" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="218" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B218" t="s">
+        <v>106</v>
+      </c>
+      <c r="G218" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H218" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I218" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="219" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B219" t="s">
+        <v>1901</v>
+      </c>
+      <c r="G219" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H219" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I219" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="220" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B220" t="s">
+        <v>108</v>
+      </c>
+      <c r="G220" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H220" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I220" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="221" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B221" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G221" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H221" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I221" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="222" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B222" t="s">
+        <v>2259</v>
+      </c>
+      <c r="G222" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H222" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I222" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="223" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B223" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G223" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H223" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I223" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="224" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B224" t="s">
+        <v>971</v>
+      </c>
+      <c r="G224" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H224" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I224" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="225" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B225" t="s">
+        <v>2260</v>
+      </c>
+      <c r="G225" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H225" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I225" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="226" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B226" t="s">
+        <v>2261</v>
+      </c>
+      <c r="G226" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H226" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I226" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="227" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B227" t="s">
+        <v>2262</v>
+      </c>
+      <c r="G227" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H227" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I227" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="228" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B228" t="s">
+        <v>2263</v>
+      </c>
+      <c r="G228" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H228" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I228" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="229" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B229" t="s">
+        <v>2264</v>
+      </c>
+      <c r="G229" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H229" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I229" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="230" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B230" t="s">
+        <v>475</v>
+      </c>
+      <c r="G230" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H230" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I230" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="231" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B231" t="s">
+        <v>2265</v>
+      </c>
+      <c r="G231" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H231" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I231" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="232" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B232" t="s">
+        <v>2266</v>
+      </c>
+      <c r="G232" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H232" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I232" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="233" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B233" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G233" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H233" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I233" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="234" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B234" t="s">
+        <v>1992</v>
+      </c>
+      <c r="G234" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H234" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I234" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="235" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B235" t="s">
+        <v>110</v>
+      </c>
+      <c r="G235" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H235" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I235" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="236" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B236" t="s">
+        <v>985</v>
+      </c>
+      <c r="G236" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H236" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I236" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="237" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B237" t="s">
+        <v>112</v>
+      </c>
+      <c r="G237" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H237" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I237" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="238" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B238" t="s">
+        <v>2267</v>
+      </c>
+      <c r="G238" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H238" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I238" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="239" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B239" t="s">
+        <v>2268</v>
+      </c>
+      <c r="G239" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H239" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I239" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="240" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B240" t="s">
+        <v>2269</v>
+      </c>
+      <c r="G240" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H240" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I240" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="241" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B241" t="s">
+        <v>2270</v>
+      </c>
+      <c r="G241" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H241" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I241" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="242" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B242" t="s">
+        <v>2271</v>
+      </c>
+      <c r="G242" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H242" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I242" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="243" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B243" t="s">
+        <v>477</v>
+      </c>
+      <c r="G243" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H243" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I243" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="244" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B244" t="s">
+        <v>2272</v>
+      </c>
+      <c r="G244" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H244" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I244" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="245" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B245" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G245" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H245" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I245" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="246" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B246" t="s">
+        <v>118</v>
+      </c>
+      <c r="G246" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H246" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I246" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="247" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B247" t="s">
+        <v>990</v>
+      </c>
+      <c r="G247" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H247" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I247" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="248" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B248" t="s">
+        <v>1323</v>
+      </c>
+      <c r="G248" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H248" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I248" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="249" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B249" t="s">
+        <v>1903</v>
+      </c>
+      <c r="G249" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H249" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I249" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="250" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B250" t="s">
+        <v>2273</v>
+      </c>
+      <c r="G250">
+        <v>2823</v>
+      </c>
+      <c r="H250" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I250" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="251" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B251" t="s">
+        <v>1833</v>
+      </c>
+      <c r="G251" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H251" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I251" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="252" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B252" t="s">
+        <v>120</v>
+      </c>
+      <c r="G252" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H252" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I252" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="253" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B253" t="s">
+        <v>992</v>
+      </c>
+      <c r="G253" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H253" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I253" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="254" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B254" t="s">
+        <v>2274</v>
+      </c>
+      <c r="G254" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H254" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I254" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="255" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B255" t="s">
+        <v>996</v>
+      </c>
+      <c r="G255" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H255" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I255" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="256" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B256" t="s">
+        <v>479</v>
+      </c>
+      <c r="G256" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H256" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I256" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="257" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B257" t="s">
+        <v>2275</v>
+      </c>
+      <c r="G257" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H257" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I257" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="258" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B258" t="s">
+        <v>2276</v>
+      </c>
+      <c r="G258" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H258" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I258" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="259" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B259" t="s">
+        <v>2277</v>
+      </c>
+      <c r="G259" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H259" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I259" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="260" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B260" t="s">
+        <v>2278</v>
+      </c>
+      <c r="G260" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H260" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I260" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="261" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B261" t="s">
+        <v>2054</v>
+      </c>
+      <c r="G261" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H261" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I261" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="262" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B262" t="s">
+        <v>2279</v>
+      </c>
+      <c r="G262" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H262" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I262" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="263" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B263" t="s">
+        <v>2280</v>
+      </c>
+      <c r="G263">
+        <v>21004</v>
+      </c>
+      <c r="H263" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I263" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="264" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B264" t="s">
+        <v>1909</v>
+      </c>
+      <c r="G264" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H264" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I264" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="265" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B265" t="s">
+        <v>2281</v>
+      </c>
+      <c r="G265" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H265" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I265" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="266" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B266" t="s">
+        <v>1458</v>
+      </c>
+      <c r="G266" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H266" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I266" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="267" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B267" t="s">
+        <v>2282</v>
+      </c>
+      <c r="G267" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H267" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I267" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="268" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B268" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G268" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H268" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I268" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="269" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B269" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G269" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H269" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I269" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="270" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B270" t="s">
+        <v>2283</v>
+      </c>
+      <c r="G270" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H270" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I270" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="271" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B271" t="s">
+        <v>130</v>
+      </c>
+      <c r="G271" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H271" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I271" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="272" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B272" t="s">
+        <v>485</v>
+      </c>
+      <c r="G272" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H272" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I272" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="273" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B273" t="s">
+        <v>2284</v>
+      </c>
+      <c r="G273" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H273" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I273" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="274" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B274" t="s">
+        <v>2285</v>
+      </c>
+      <c r="G274" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H274" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I274" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="275" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B275" t="s">
+        <v>487</v>
+      </c>
+      <c r="G275" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H275" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I275" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="276" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B276" t="s">
+        <v>2286</v>
+      </c>
+      <c r="G276" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H276" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I276" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="277" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B277" t="s">
+        <v>272</v>
+      </c>
+      <c r="G277" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H277" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I277" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="278" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B278" t="s">
+        <v>2287</v>
+      </c>
+      <c r="G278" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H278" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I278" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="279" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B279" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G279" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H279" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I279" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="280" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B280" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G280" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H280" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I280" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="281" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B281" t="s">
+        <v>136</v>
+      </c>
+      <c r="G281" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H281" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I281" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="282" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B282" t="s">
+        <v>2288</v>
+      </c>
+      <c r="G282" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H282" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I282" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="283" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B283" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G283" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H283" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I283" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="284" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B284" t="s">
+        <v>1998</v>
+      </c>
+      <c r="G284" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H284" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I284" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="285" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B285" t="s">
+        <v>658</v>
+      </c>
+      <c r="G285" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H285" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I285" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="286" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B286" t="s">
+        <v>138</v>
+      </c>
+      <c r="G286" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H286" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I286" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="287" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B287" t="s">
+        <v>1466</v>
+      </c>
+      <c r="G287" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H287" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I287" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="288" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B288" t="s">
+        <v>834</v>
+      </c>
+      <c r="G288" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H288" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I288" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="289" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B289" t="s">
+        <v>2289</v>
+      </c>
+      <c r="G289" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H289" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I289" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="290" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B290" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G290">
+        <v>0</v>
+      </c>
+      <c r="H290" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I290" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="291" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B291" t="s">
+        <v>660</v>
+      </c>
+      <c r="G291" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H291" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I291" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="292" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B292" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G292" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H292" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I292" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="293" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B293" t="s">
+        <v>848</v>
+      </c>
+      <c r="G293" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H293" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I293" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="294" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B294" t="s">
+        <v>2114</v>
+      </c>
+      <c r="G294" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H294" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I294" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="295" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B295" t="s">
+        <v>1234</v>
+      </c>
+      <c r="G295" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H295" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I295" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="296" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B296" t="s">
+        <v>1569</v>
+      </c>
+      <c r="G296">
+        <v>0</v>
+      </c>
+      <c r="H296" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I296" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="297" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B297" t="s">
+        <v>2165</v>
+      </c>
+      <c r="G297" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H297" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I297" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="298" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B298" t="s">
+        <v>759</v>
+      </c>
+      <c r="G298" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H298" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I298" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="299" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B299" t="s">
+        <v>1618</v>
+      </c>
+      <c r="G299" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H299" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I299" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="300" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B300" t="s">
+        <v>2290</v>
+      </c>
+      <c r="G300" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H300" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I300" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="301" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B301" t="s">
+        <v>2291</v>
+      </c>
+      <c r="G301" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H301" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I301" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="302" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B302" t="s">
+        <v>761</v>
+      </c>
+      <c r="G302" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H302" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I302" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="303" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B303" t="s">
+        <v>494</v>
+      </c>
+      <c r="G303" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H303" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I303" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="304" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B304" t="s">
+        <v>1641</v>
+      </c>
+      <c r="G304" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H304" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I304" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="305" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B305" t="s">
+        <v>2292</v>
+      </c>
+      <c r="G305" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H305" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I305" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="306" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B306" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G306" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H306" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I306" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="307" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B307" t="s">
+        <v>2293</v>
+      </c>
+      <c r="G307" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H307" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I307" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="308" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B308" t="s">
+        <v>2108</v>
+      </c>
+      <c r="G308">
+        <v>0</v>
+      </c>
+      <c r="H308" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I308" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="309" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B309" t="s">
+        <v>2294</v>
+      </c>
+      <c r="G309" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H309" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I309" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="310" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B310" t="s">
+        <v>144</v>
+      </c>
+      <c r="G310" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H310" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I310" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="311" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B311" t="s">
+        <v>877</v>
+      </c>
+      <c r="G311" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H311" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I311" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="312" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B312" t="s">
+        <v>1836</v>
+      </c>
+      <c r="G312" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H312" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I312" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="313" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B313" t="s">
+        <v>1571</v>
+      </c>
+      <c r="G313" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H313" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I313" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="314" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B314" t="s">
+        <v>274</v>
+      </c>
+      <c r="G314" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H314" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I314" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="315" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B315" t="s">
+        <v>2295</v>
+      </c>
+      <c r="G315" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H315" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I315" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="316" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B316" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G316" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H316" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I316" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="317" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B317" t="s">
+        <v>2296</v>
+      </c>
+      <c r="G317" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H317" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I317" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="318" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B318" t="s">
+        <v>343</v>
+      </c>
+      <c r="G318" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H318" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I318" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="319" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B319" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G319" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H319" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I319" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="320" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B320" t="s">
+        <v>2297</v>
+      </c>
+      <c r="G320" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H320" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I320" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="321" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B321" t="s">
+        <v>276</v>
+      </c>
+      <c r="G321" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H321" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I321" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="322" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B322" t="s">
+        <v>1291</v>
+      </c>
+      <c r="G322" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H322" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I322" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="323" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B323" t="s">
+        <v>2298</v>
+      </c>
+      <c r="G323" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H323" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I323" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="324" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B324" t="s">
+        <v>2299</v>
+      </c>
+      <c r="G324" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H324" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I324" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="325" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B325" t="s">
+        <v>644</v>
+      </c>
+      <c r="G325" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H325" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I325" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="326" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B326" t="s">
+        <v>662</v>
+      </c>
+      <c r="G326" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H326" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I326" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="327" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B327" t="s">
+        <v>2300</v>
+      </c>
+      <c r="G327" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H327" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I327" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="328" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B328" t="s">
+        <v>148</v>
+      </c>
+      <c r="G328" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H328" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I328" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="329" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B329" t="s">
+        <v>2301</v>
+      </c>
+      <c r="G329" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H329" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I329" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="330" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B330" t="s">
+        <v>666</v>
+      </c>
+      <c r="G330" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H330" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I330" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="331" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B331" t="s">
+        <v>1643</v>
+      </c>
+      <c r="G331" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H331" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I331" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="332" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B332" t="s">
+        <v>1748</v>
+      </c>
+      <c r="G332" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H332" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I332" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="333" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B333" t="s">
+        <v>2302</v>
+      </c>
+      <c r="G333" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H333" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I333" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="334" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B334" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G334" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H334" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I334" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="335" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B335" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G335" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H335" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I335" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="336" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B336" t="s">
+        <v>1384</v>
+      </c>
+      <c r="G336" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H336" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I336" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="337" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B337" t="s">
+        <v>504</v>
+      </c>
+      <c r="G337" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H337" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I337" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="338" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B338" t="s">
+        <v>767</v>
+      </c>
+      <c r="G338" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H338" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I338" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="339" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B339" t="s">
+        <v>2303</v>
+      </c>
+      <c r="G339" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H339" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I339" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="340" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B340" t="s">
+        <v>2304</v>
+      </c>
+      <c r="G340" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H340" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I340" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="341" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B341" t="s">
+        <v>2084</v>
+      </c>
+      <c r="G341" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H341" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I341" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="342" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B342" t="s">
+        <v>2305</v>
+      </c>
+      <c r="G342" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H342" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I342" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="343" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B343" t="s">
+        <v>2306</v>
+      </c>
+      <c r="G343" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H343" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I343" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="344" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B344" t="s">
+        <v>2307</v>
+      </c>
+      <c r="G344" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H344" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I344" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="345" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B345" t="s">
+        <v>150</v>
+      </c>
+      <c r="G345" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H345" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I345" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="346" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B346" t="s">
+        <v>2308</v>
+      </c>
+      <c r="G346" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H346" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I346" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="347" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B347" t="s">
+        <v>1620</v>
+      </c>
+      <c r="G347" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H347" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I347" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="348" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B348" t="s">
+        <v>2309</v>
+      </c>
+      <c r="G348" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H348" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I348" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="349" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B349" t="s">
+        <v>2060</v>
+      </c>
+      <c r="G349" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H349" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I349" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="350" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B350" t="s">
+        <v>353</v>
+      </c>
+      <c r="G350" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H350" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I350" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="351" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B351" t="s">
+        <v>716</v>
+      </c>
+      <c r="G351" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H351" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I351" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="352" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B352" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G352" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H352" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I352" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="353" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B353" t="s">
+        <v>1919</v>
+      </c>
+      <c r="G353" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H353" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I353" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="354" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B354" t="s">
+        <v>2310</v>
+      </c>
+      <c r="G354" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H354" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I354" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="355" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B355" t="s">
+        <v>514</v>
+      </c>
+      <c r="G355" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H355" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I355" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="356" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B356" t="s">
+        <v>156</v>
+      </c>
+      <c r="G356" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H356" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I356" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="357" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B357" t="s">
+        <v>1921</v>
+      </c>
+      <c r="G357" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H357" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I357" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="358" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B358" t="s">
+        <v>2311</v>
+      </c>
+      <c r="G358" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H358" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I358" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="359" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B359" t="s">
+        <v>670</v>
+      </c>
+      <c r="G359" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H359" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I359" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="360" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B360" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G360" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H360" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I360" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="361" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B361" t="s">
+        <v>2312</v>
+      </c>
+      <c r="G361" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H361" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I361" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="362" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B362" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G362" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H362" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I362" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="363" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B363" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G363" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H363" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I363" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="364" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B364" t="s">
+        <v>516</v>
+      </c>
+      <c r="G364" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H364" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I364" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="365" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B365" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G365" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H365" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I365" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="366" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B366" t="s">
+        <v>672</v>
+      </c>
+      <c r="G366" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H366" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I366" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="367" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B367" t="s">
+        <v>2313</v>
+      </c>
+      <c r="G367" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H367" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I367" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="368" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B368" t="s">
+        <v>2314</v>
+      </c>
+      <c r="G368">
+        <v>3127</v>
+      </c>
+      <c r="H368" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I368" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="369" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B369" t="s">
+        <v>2002</v>
+      </c>
+      <c r="G369" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H369" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I369" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="370" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B370" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G370" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H370" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I370" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="371" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B371" t="s">
+        <v>1756</v>
+      </c>
+      <c r="G371" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H371" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I371" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="372" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B372" t="s">
+        <v>162</v>
+      </c>
+      <c r="G372" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H372" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I372" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="373" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B373" t="s">
+        <v>1758</v>
+      </c>
+      <c r="G373" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H373" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I373" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="374" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B374" t="s">
+        <v>1238</v>
+      </c>
+      <c r="G374" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H374" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I374" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="375" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B375" t="s">
+        <v>2087</v>
+      </c>
+      <c r="G375" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H375" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I375" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="376" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B376" t="s">
+        <v>2315</v>
+      </c>
+      <c r="G376" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H376" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I376" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="377" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B377" t="s">
+        <v>1923</v>
+      </c>
+      <c r="G377" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H377" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I377" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="378" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B378" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G378" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H378" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I378" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="379" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B379" t="s">
+        <v>2316</v>
+      </c>
+      <c r="G379" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H379" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I379" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="380" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B380" t="s">
+        <v>770</v>
+      </c>
+      <c r="G380" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H380" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I380" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="381" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B381" t="s">
+        <v>840</v>
+      </c>
+      <c r="G381" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H381" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I381" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="382" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B382" t="s">
+        <v>528</v>
+      </c>
+      <c r="G382" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H382" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I382" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="383" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B383" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G383" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H383" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I383" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="384" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B384" t="s">
+        <v>676</v>
+      </c>
+      <c r="G384" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H384" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I384" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="385" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B385" t="s">
+        <v>280</v>
+      </c>
+      <c r="G385" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H385" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I385" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="386" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B386" t="s">
+        <v>2004</v>
+      </c>
+      <c r="G386" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H386" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I386" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="387" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B387" t="s">
+        <v>1925</v>
+      </c>
+      <c r="G387" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H387" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I387" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="388" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B388" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G388" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H388" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I388" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="389" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B389" t="s">
+        <v>1581</v>
+      </c>
+      <c r="G389" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H389" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I389" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="390" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B390" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G390" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H390" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I390" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="391" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B391" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G391" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H391" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I391" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="392" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B392" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G392" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H392" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I392" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="393" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B393" t="s">
+        <v>1412</v>
+      </c>
+      <c r="G393">
+        <v>33684</v>
+      </c>
+      <c r="H393" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I393" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="394" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B394" t="s">
+        <v>2317</v>
+      </c>
+      <c r="G394" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H394" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I394" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="395" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B395" t="s">
+        <v>536</v>
+      </c>
+      <c r="G395" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H395" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I395" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="396" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B396" t="s">
+        <v>2066</v>
+      </c>
+      <c r="G396" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H396" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I396" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="397" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B397" t="s">
+        <v>2318</v>
+      </c>
+      <c r="G397" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H397" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I397" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="398" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B398" t="s">
+        <v>842</v>
+      </c>
+      <c r="G398" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H398" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I398" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="399" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B399" t="s">
+        <v>164</v>
+      </c>
+      <c r="G399" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H399" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I399" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="400" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B400" t="s">
+        <v>1628</v>
+      </c>
+      <c r="G400">
+        <v>3001</v>
+      </c>
+      <c r="H400" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I400" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="401" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B401" t="s">
+        <v>540</v>
+      </c>
+      <c r="G401" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H401" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I401" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="402" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B402" t="s">
+        <v>1766</v>
+      </c>
+      <c r="G402" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H402" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I402" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="403" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B403" t="s">
+        <v>1927</v>
+      </c>
+      <c r="G403" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H403" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I403" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="404" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B404" t="s">
+        <v>2319</v>
+      </c>
+      <c r="G404" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H404" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I404" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="405" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B405" t="s">
+        <v>1622</v>
+      </c>
+      <c r="G405" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H405" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I405" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="406" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B406" t="s">
+        <v>2320</v>
+      </c>
+      <c r="G406" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H406" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I406" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="407" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B407" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G407" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H407" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I407" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="408" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B408" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G408" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H408" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I408" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="409" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B409" t="s">
+        <v>1929</v>
+      </c>
+      <c r="G409" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H409" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I409" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="410" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B410" t="s">
+        <v>887</v>
+      </c>
+      <c r="G410" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H410" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I410" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="411" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B411" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G411" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H411" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I411" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="412" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B412" t="s">
+        <v>1491</v>
+      </c>
+      <c r="G412" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H412" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I412" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="413" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B413" t="s">
+        <v>284</v>
+      </c>
+      <c r="G413" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H413" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I413" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="414" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B414" t="s">
+        <v>286</v>
+      </c>
+      <c r="G414" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H414" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I414" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="415" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B415" t="s">
+        <v>2321</v>
+      </c>
+      <c r="G415" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H415" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I415" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="416" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B416" t="s">
+        <v>2068</v>
+      </c>
+      <c r="G416" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H416" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I416" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="417" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B417" t="s">
+        <v>2006</v>
+      </c>
+      <c r="G417" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H417" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I417" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="418" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B418" t="s">
+        <v>1931</v>
+      </c>
+      <c r="G418" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H418" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I418" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="419" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B419" t="s">
+        <v>1495</v>
+      </c>
+      <c r="G419" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H419" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I419" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="420" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B420" t="s">
+        <v>2322</v>
+      </c>
+      <c r="G420" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H420" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I420" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="421" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B421" t="s">
+        <v>1647</v>
+      </c>
+      <c r="G421" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H421" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I421" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="422" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B422" t="s">
+        <v>168</v>
+      </c>
+      <c r="G422" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H422" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I422" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="423" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B423" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G423" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H423" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I423" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="424" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B424" t="s">
+        <v>1770</v>
+      </c>
+      <c r="G424" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H424" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I424" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="425" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B425" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G425" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H425" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I425" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="426" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B426" t="s">
+        <v>2323</v>
+      </c>
+      <c r="G426" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H426" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I426" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="427" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B427" t="s">
+        <v>2324</v>
+      </c>
+      <c r="G427" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H427" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I427" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="428" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B428" t="s">
+        <v>2325</v>
+      </c>
+      <c r="G428" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H428" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I428" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="429" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B429" t="s">
+        <v>2091</v>
+      </c>
+      <c r="G429" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H429" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I429" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="430" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B430" t="s">
+        <v>2163</v>
+      </c>
+      <c r="G430">
+        <v>134</v>
+      </c>
+      <c r="H430" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I430" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="431" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B431" t="s">
+        <v>288</v>
+      </c>
+      <c r="G431" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H431" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I431" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="432" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B432" t="s">
+        <v>2326</v>
+      </c>
+      <c r="G432" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H432" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I432" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="433" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B433" t="s">
+        <v>2327</v>
+      </c>
+      <c r="G433" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H433" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I433" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="434" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B434" t="s">
+        <v>2328</v>
+      </c>
+      <c r="G434" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H434" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I434" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="435" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B435" t="s">
+        <v>2329</v>
+      </c>
+      <c r="G435" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H435" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I435" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="436" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B436" t="s">
+        <v>2330</v>
+      </c>
+      <c r="G436" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H436" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I436" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="437" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B437" t="s">
+        <v>1398</v>
+      </c>
+      <c r="G437" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H437" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I437" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="438" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B438" t="s">
+        <v>2331</v>
+      </c>
+      <c r="G438" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H438" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I438" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="439" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B439" t="s">
+        <v>2123</v>
+      </c>
+      <c r="G439" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H439" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I439" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="440" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B440" t="s">
+        <v>718</v>
+      </c>
+      <c r="G440" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="H440" s="9" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I440" s="9" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="441" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B441" t="s">
+        <v>1049</v>
       </c>
     </row>
   </sheetData>
